--- a/output/Tables/Modal shift/HIA_modal_shift_100replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_100replicate.xlsx
@@ -434,40 +434,40 @@
         <v>0.5</v>
       </c>
       <c r="C2">
-        <v>9752450.282236822</v>
+        <v>9828968.673715824</v>
       </c>
       <c r="D2">
-        <v>10299352.43785919</v>
+        <v>10381320.89266793</v>
       </c>
       <c r="E2">
-        <v>11038909.57421522</v>
+        <v>11128247.9638243</v>
       </c>
       <c r="F2">
-        <v>40800861.24582278</v>
+        <v>42106702.840769</v>
       </c>
       <c r="G2">
-        <v>43229925.50368554</v>
+        <v>44623143.57522763</v>
       </c>
       <c r="H2">
-        <v>45875899.51782789</v>
+        <v>47364296.58093911</v>
       </c>
       <c r="I2">
-        <v>110410.8212389555</v>
+        <v>109938.706846395</v>
       </c>
       <c r="J2">
-        <v>119212.7686546875</v>
+        <v>118716.8422720633</v>
       </c>
       <c r="K2">
-        <v>126265.7945308117</v>
+        <v>125750.7875318024</v>
       </c>
       <c r="L2">
-        <v>5396616.212620417</v>
+        <v>5569217.664348083</v>
       </c>
       <c r="M2">
-        <v>5745912.346485482</v>
+        <v>5931078.416611733</v>
       </c>
       <c r="N2">
-        <v>6095435.463032216</v>
+        <v>6293174.316407739</v>
       </c>
     </row>
   </sheetData>
